--- a/IM/202610_Service_Count_Report.xlsx
+++ b/IM/202610_Service_Count_Report.xlsx
@@ -11,14 +11,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Report'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$79</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$90</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="284">
   <si>
     <t>服務次數統計表        篩選月份：202610</t>
   </si>
@@ -233,6 +233,42 @@
     <t>天玉街</t>
   </si>
   <si>
+    <t>2026-10-02</t>
+  </si>
+  <si>
+    <t>14:50:00</t>
+  </si>
+  <si>
+    <t>15:13:00</t>
+  </si>
+  <si>
+    <t>T352800006</t>
+  </si>
+  <si>
+    <t>eS-3528A 黑白複合機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">中原造像股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市中和區建康路130號7樓-11</t>
+  </si>
+  <si>
+    <t>14:25:00</t>
+  </si>
+  <si>
+    <t>14:45:00</t>
+  </si>
+  <si>
+    <t>T352800007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">中康彩色印刷事業股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市中和區建二路56號</t>
+  </si>
+  <si>
     <t>10:10:00</t>
   </si>
   <si>
@@ -251,9 +287,6 @@
     <t>台北市北投區明德路200號</t>
   </si>
   <si>
-    <t>2026-10-02</t>
-  </si>
-  <si>
     <t>10:38:00</t>
   </si>
   <si>
@@ -350,6 +383,21 @@
     <t>三重太璞宮</t>
   </si>
   <si>
+    <t>15:47:00</t>
+  </si>
+  <si>
+    <t>16:10:00</t>
+  </si>
+  <si>
+    <t>THILF0C660</t>
+  </si>
+  <si>
+    <t>新北市中和區中和路414號</t>
+  </si>
+  <si>
+    <t>中和永安市場</t>
+  </si>
+  <si>
     <t>15:27:00</t>
   </si>
   <si>
@@ -509,15 +557,33 @@
     <t>新北市淡水區中正路28號4樓(淡水)</t>
   </si>
   <si>
+    <t>15:11:00</t>
+  </si>
+  <si>
+    <t>15:16:00</t>
+  </si>
+  <si>
+    <t>T352500087</t>
+  </si>
+  <si>
+    <t>eS-3525AC 彩色複合機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鋐原能源股份有限公司 </t>
+  </si>
+  <si>
+    <t>桃園市蘆竹區機捷路二段646號1樓</t>
+  </si>
+  <si>
+    <t>蘆竹</t>
+  </si>
+  <si>
     <t>13:10:00</t>
   </si>
   <si>
     <t>T352500149</t>
   </si>
   <si>
-    <t>eS-3525AC 彩色複合機</t>
-  </si>
-  <si>
     <t xml:space="preserve">東南旅行社股份有限公司 </t>
   </si>
   <si>
@@ -578,6 +644,21 @@
     <t>三重</t>
   </si>
   <si>
+    <t>15:30:00</t>
+  </si>
+  <si>
+    <t>T301800078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">台灣大哥大股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市五股區五權路48號2樓(五股倉庫)</t>
+  </si>
+  <si>
+    <t>五股倉庫(黑)</t>
+  </si>
+  <si>
     <t>08:30:00</t>
   </si>
   <si>
@@ -611,9 +692,6 @@
     <t>T302800029</t>
   </si>
   <si>
-    <t xml:space="preserve">台灣大哥大股份有限公司 </t>
-  </si>
-  <si>
     <t>新北市三重區重新路5段609巷2號3樓</t>
   </si>
   <si>
@@ -650,18 +728,48 @@
     <t>跟換radf分離輪</t>
   </si>
   <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>T351800123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">優耐特精密機械股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市三重區興德路94號</t>
+  </si>
+  <si>
+    <t xml:space="preserve">檢測為鐳射模組待更換 </t>
+  </si>
+  <si>
+    <t>17:30:00</t>
+  </si>
+  <si>
+    <t>pm</t>
+  </si>
+  <si>
     <t>14:00:00</t>
   </si>
   <si>
+    <t>T352500250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">宏偉營造股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市三重區光復路1段61巷26號2樓</t>
+  </si>
+  <si>
     <t>14:30:00</t>
   </si>
   <si>
     <t>T352800011</t>
   </si>
   <si>
-    <t>eS-3528A 黑白複合機</t>
-  </si>
-  <si>
     <t xml:space="preserve">全聯實業股份有限公司 </t>
   </si>
   <si>
@@ -728,9 +836,6 @@
     <t>台北客服4樓-2LJ15(黑)</t>
   </si>
   <si>
-    <t>15:30:00</t>
-  </si>
-  <si>
     <t>T452800033</t>
   </si>
   <si>
@@ -756,9 +861,6 @@
   </si>
   <si>
     <t>更換鈔票夾</t>
-  </si>
-  <si>
-    <t>17:00:00</t>
   </si>
   <si>
     <t>狄澤洋</t>
@@ -1193,7 +1295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB79"/>
+  <dimension ref="A1:AB90"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -1897,7 +1999,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="7">
-        <v>2026100032</v>
+        <v>2026100530</v>
       </c>
       <c r="C11" s="7">
         <v>1</v>
@@ -1909,50 +2011,46 @@
         <v>30</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N11" s="8"/>
       <c r="O11" s="7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7">
-        <v>142509</v>
-      </c>
-      <c r="S11" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>173697</v>
+      </c>
+      <c r="S11" s="7"/>
       <c r="T11" s="7"/>
       <c r="U11" s="7"/>
       <c r="V11" s="7"/>
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
       <c r="Y11" s="7"/>
-      <c r="Z11" s="8" t="s">
-        <v>49</v>
-      </c>
+      <c r="Z11" s="8"/>
       <c r="AA11" s="7" t="s">
         <v>41</v>
       </c>
@@ -1965,7 +2063,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>2026100033</v>
+        <v>2026100493</v>
       </c>
       <c r="C12" s="3">
         <v>1</v>
@@ -1977,28 +2075,28 @@
         <v>30</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="N12" s="6"/>
       <c r="O12" s="3" t="s">
@@ -2007,7 +2105,7 @@
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3">
-        <v>142509</v>
+        <v>307213</v>
       </c>
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
@@ -2016,20 +2114,20 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
-      <c r="Z12" s="6" t="s">
-        <v>49</v>
-      </c>
+      <c r="Z12" s="6"/>
       <c r="AA12" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB12" s="3"/>
+      <c r="AB12" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:28">
       <c r="A13" s="7">
         <v>11</v>
       </c>
       <c r="B13" s="7">
-        <v>2026100425</v>
+        <v>2026100032</v>
       </c>
       <c r="C13" s="7">
         <v>1</v>
@@ -2041,35 +2139,37 @@
         <v>30</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
+        <v>81</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L13" s="8" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="N13" s="8" t="s">
-        <v>79</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N13" s="8"/>
       <c r="O13" s="7" t="s">
         <v>48</v>
       </c>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7">
-        <v>0</v>
+        <v>142509</v>
       </c>
       <c r="S13" s="7" t="s">
         <v>41</v>
@@ -2079,11 +2179,9 @@
       <c r="V13" s="7"/>
       <c r="W13" s="7"/>
       <c r="X13" s="7"/>
-      <c r="Y13" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y13" s="7"/>
       <c r="Z13" s="8" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="AA13" s="7" t="s">
         <v>41</v>
@@ -2097,7 +2195,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>2026100249</v>
+        <v>2026100033</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
@@ -2109,39 +2207,37 @@
         <v>30</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H14" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>82</v>
       </c>
       <c r="K14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L14" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="L14" s="6" t="s">
-        <v>77</v>
-      </c>
       <c r="M14" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>79</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N14" s="6"/>
       <c r="O14" s="3" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3">
-        <v>0</v>
+        <v>142509</v>
       </c>
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
@@ -2151,7 +2247,7 @@
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="6" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>41</v>
@@ -2163,7 +2259,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="7">
-        <v>2026100248</v>
+        <v>2026100425</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
@@ -2175,21 +2271,21 @@
         <v>30</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G15" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H15" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="I15" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>88</v>
       </c>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
       <c r="L15" s="8" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="M15" s="8" t="s">
         <v>89</v>
@@ -2217,7 +2313,7 @@
         <v>41</v>
       </c>
       <c r="Z15" s="8" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AA15" s="7" t="s">
         <v>41</v>
@@ -2231,7 +2327,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>2026100397</v>
+        <v>2026100249</v>
       </c>
       <c r="C16" s="3">
         <v>1</v>
@@ -2243,63 +2339,61 @@
         <v>30</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>92</v>
       </c>
       <c r="I16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
+      <c r="K16" s="3" t="s">
+        <v>94</v>
+      </c>
       <c r="L16" s="6" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="N16" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="O16" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3">
         <v>0</v>
       </c>
-      <c r="S16" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-      <c r="Y16" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y16" s="3"/>
       <c r="Z16" s="6" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="AA16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB16" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB16" s="3"/>
     </row>
     <row r="17" spans="1:28">
       <c r="A17" s="7">
         <v>15</v>
       </c>
       <c r="B17" s="7">
-        <v>2026100447</v>
+        <v>2026100248</v>
       </c>
       <c r="C17" s="7">
         <v>1</v>
@@ -2311,27 +2405,27 @@
         <v>30</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
       <c r="L17" s="8" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O17" s="7" t="s">
         <v>48</v>
@@ -2353,7 +2447,7 @@
         <v>41</v>
       </c>
       <c r="Z17" s="8" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AA17" s="7" t="s">
         <v>41</v>
@@ -2367,7 +2461,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>2026100458</v>
+        <v>2026100397</v>
       </c>
       <c r="C18" s="3">
         <v>1</v>
@@ -2379,27 +2473,27 @@
         <v>30</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="6" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>48</v>
@@ -2421,7 +2515,7 @@
         <v>41</v>
       </c>
       <c r="Z18" s="6" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>41</v>
@@ -2435,7 +2529,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="7">
-        <v>2026100251</v>
+        <v>2026100447</v>
       </c>
       <c r="C19" s="7">
         <v>1</v>
@@ -2447,27 +2541,27 @@
         <v>30</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
       <c r="L19" s="8" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N19" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O19" s="7" t="s">
         <v>48</v>
@@ -2489,7 +2583,7 @@
         <v>41</v>
       </c>
       <c r="Z19" s="8" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AA19" s="7" t="s">
         <v>41</v>
@@ -2503,7 +2597,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>2026100451</v>
+        <v>2026100458</v>
       </c>
       <c r="C20" s="3">
         <v>1</v>
@@ -2515,27 +2609,27 @@
         <v>30</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
       <c r="L20" s="6" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>48</v>
@@ -2557,7 +2651,7 @@
         <v>41</v>
       </c>
       <c r="Z20" s="6" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AA20" s="3" t="s">
         <v>41</v>
@@ -2571,7 +2665,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="7">
-        <v>2026100398</v>
+        <v>2026100651</v>
       </c>
       <c r="C21" s="7">
         <v>1</v>
@@ -2580,28 +2674,24 @@
         <v>29</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>116</v>
+        <v>30</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
       <c r="L21" s="8" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="M21" s="8" t="s">
         <v>120</v>
@@ -2612,14 +2702,10 @@
       <c r="O21" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="P21" s="7">
-        <v>8200</v>
-      </c>
-      <c r="Q21" s="7">
-        <v>18671</v>
-      </c>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
       <c r="R21" s="7">
-        <v>26952</v>
+        <v>0</v>
       </c>
       <c r="S21" s="7" t="s">
         <v>41</v>
@@ -2629,9 +2715,11 @@
       <c r="V21" s="7"/>
       <c r="W21" s="7"/>
       <c r="X21" s="7"/>
-      <c r="Y21" s="7"/>
+      <c r="Y21" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="Z21" s="8" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="AA21" s="7" t="s">
         <v>41</v>
@@ -2645,7 +2733,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>2026100399</v>
+        <v>2026100251</v>
       </c>
       <c r="C22" s="3">
         <v>1</v>
@@ -2654,68 +2742,66 @@
         <v>29</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>116</v>
+        <v>30</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
       <c r="L22" s="6" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P22" s="3">
-        <v>8200</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>18671</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
       <c r="R22" s="3">
-        <v>26952</v>
-      </c>
-      <c r="S22" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
-      <c r="Y22" s="3"/>
+      <c r="Y22" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="Z22" s="6" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB22" s="3"/>
+      <c r="AB22" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:28">
       <c r="A23" s="7">
         <v>21</v>
       </c>
       <c r="B23" s="7">
-        <v>2026100441</v>
+        <v>2026100451</v>
       </c>
       <c r="C23" s="7">
         <v>1</v>
@@ -2724,44 +2810,38 @@
         <v>29</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>116</v>
+        <v>30</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
       <c r="L23" s="8" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="N23" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="O23" s="7" t="s">
         <v>48</v>
       </c>
       <c r="P23" s="7"/>
-      <c r="Q23" s="7">
-        <v>3179</v>
-      </c>
+      <c r="Q23" s="7"/>
       <c r="R23" s="7">
-        <v>176877</v>
+        <v>0</v>
       </c>
       <c r="S23" s="7" t="s">
         <v>41</v>
@@ -2771,19 +2851,25 @@
       <c r="V23" s="7"/>
       <c r="W23" s="7"/>
       <c r="X23" s="7"/>
-      <c r="Y23" s="7"/>
+      <c r="Y23" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="Z23" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA23" s="7"/>
-      <c r="AB23" s="7"/>
+        <v>91</v>
+      </c>
+      <c r="AA23" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB23" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:28">
       <c r="A24" s="3">
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>2026100442</v>
+        <v>2026100398</v>
       </c>
       <c r="C24" s="3">
         <v>1</v>
@@ -2792,19 +2878,19 @@
         <v>29</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>35</v>
@@ -2813,25 +2899,29 @@
         <v>36</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P24" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="P24" s="3">
+        <v>8200</v>
+      </c>
       <c r="Q24" s="3">
-        <v>3179</v>
+        <v>18671</v>
       </c>
       <c r="R24" s="3">
-        <v>176877</v>
-      </c>
-      <c r="S24" s="3"/>
+        <v>26952</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
@@ -2839,17 +2929,21 @@
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
       <c r="Z24" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA24" s="3"/>
-      <c r="AB24" s="3"/>
+        <v>138</v>
+      </c>
+      <c r="AA24" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:28">
       <c r="A25" s="7">
         <v>23</v>
       </c>
       <c r="B25" s="7">
-        <v>2026100445</v>
+        <v>2026100399</v>
       </c>
       <c r="C25" s="7">
         <v>1</v>
@@ -2858,19 +2952,19 @@
         <v>29</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J25" s="7" t="s">
         <v>35</v>
@@ -2879,25 +2973,27 @@
         <v>36</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="N25" s="8"/>
+        <v>136</v>
+      </c>
+      <c r="N25" s="8" t="s">
+        <v>137</v>
+      </c>
       <c r="O25" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="P25" s="7"/>
+        <v>40</v>
+      </c>
+      <c r="P25" s="7">
+        <v>8200</v>
+      </c>
       <c r="Q25" s="7">
-        <v>722</v>
+        <v>18671</v>
       </c>
       <c r="R25" s="7">
-        <v>31746</v>
-      </c>
-      <c r="S25" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>26952</v>
+      </c>
+      <c r="S25" s="7"/>
       <c r="T25" s="7"/>
       <c r="U25" s="7"/>
       <c r="V25" s="7"/>
@@ -2905,21 +3001,19 @@
       <c r="X25" s="7"/>
       <c r="Y25" s="7"/>
       <c r="Z25" s="8" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="AA25" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB25" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB25" s="7"/>
     </row>
     <row r="26" spans="1:28">
       <c r="A26" s="3">
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>2026100446</v>
+        <v>2026100441</v>
       </c>
       <c r="C26" s="3">
         <v>1</v>
@@ -2928,19 +3022,19 @@
         <v>29</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>35</v>
@@ -2949,23 +3043,27 @@
         <v>36</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="N26" s="6"/>
+        <v>143</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>144</v>
+      </c>
       <c r="O26" s="3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="P26" s="3"/>
       <c r="Q26" s="3">
-        <v>722</v>
+        <v>3179</v>
       </c>
       <c r="R26" s="3">
-        <v>31746</v>
-      </c>
-      <c r="S26" s="3"/>
+        <v>176877</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
@@ -2973,11 +3071,9 @@
       <c r="X26" s="3"/>
       <c r="Y26" s="3"/>
       <c r="Z26" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA26" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AA26" s="3"/>
       <c r="AB26" s="3"/>
     </row>
     <row r="27" spans="1:28">
@@ -2985,7 +3081,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="7">
-        <v>2026100084</v>
+        <v>2026100442</v>
       </c>
       <c r="C27" s="7">
         <v>1</v>
@@ -2994,46 +3090,46 @@
         <v>29</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>137</v>
+        <v>35</v>
       </c>
       <c r="K27" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="N27" s="8" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="O27" s="7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="P27" s="7"/>
-      <c r="Q27" s="7"/>
+      <c r="Q27" s="7">
+        <v>3179</v>
+      </c>
       <c r="R27" s="7">
-        <v>30982</v>
-      </c>
-      <c r="S27" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>176877</v>
+      </c>
+      <c r="S27" s="7"/>
       <c r="T27" s="7"/>
       <c r="U27" s="7"/>
       <c r="V27" s="7"/>
@@ -3041,21 +3137,17 @@
       <c r="X27" s="7"/>
       <c r="Y27" s="7"/>
       <c r="Z27" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA27" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB27" s="7">
-        <v>1</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AA27" s="7"/>
+      <c r="AB27" s="7"/>
     </row>
     <row r="28" spans="1:28">
       <c r="A28" s="3">
         <v>26</v>
       </c>
       <c r="B28" s="3">
-        <v>2026100085</v>
+        <v>2026100445</v>
       </c>
       <c r="C28" s="3">
         <v>1</v>
@@ -3064,44 +3156,46 @@
         <v>29</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>137</v>
+        <v>35</v>
       </c>
       <c r="K28" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="N28" s="6" t="s">
-        <v>140</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="N28" s="6"/>
       <c r="O28" s="3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
+      <c r="Q28" s="3">
+        <v>722</v>
+      </c>
       <c r="R28" s="3">
-        <v>30982</v>
-      </c>
-      <c r="S28" s="3"/>
+        <v>31746</v>
+      </c>
+      <c r="S28" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
@@ -3109,19 +3203,21 @@
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
       <c r="Z28" s="6" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="AA28" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB28" s="3"/>
+      <c r="AB28" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:28">
       <c r="A29" s="7">
         <v>27</v>
       </c>
       <c r="B29" s="7">
-        <v>2026100071</v>
+        <v>2026100446</v>
       </c>
       <c r="C29" s="7">
         <v>1</v>
@@ -3130,44 +3226,44 @@
         <v>29</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>75</v>
+        <v>145</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="K29" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="N29" s="8"/>
       <c r="O29" s="7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="P29" s="7"/>
-      <c r="Q29" s="7"/>
+      <c r="Q29" s="7">
+        <v>722</v>
+      </c>
       <c r="R29" s="7">
-        <v>40400</v>
-      </c>
-      <c r="S29" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>31746</v>
+      </c>
+      <c r="S29" s="7"/>
       <c r="T29" s="7"/>
       <c r="U29" s="7"/>
       <c r="V29" s="7"/>
@@ -3175,21 +3271,19 @@
       <c r="X29" s="7"/>
       <c r="Y29" s="7"/>
       <c r="Z29" s="8" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="AA29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB29" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB29" s="7"/>
     </row>
     <row r="30" spans="1:28">
       <c r="A30" s="3">
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>2026100072</v>
+        <v>2026100084</v>
       </c>
       <c r="C30" s="3">
         <v>1</v>
@@ -3198,42 +3292,46 @@
         <v>29</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>63</v>
+        <v>153</v>
       </c>
       <c r="K30" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="N30" s="6"/>
+        <v>155</v>
+      </c>
+      <c r="N30" s="6" t="s">
+        <v>156</v>
+      </c>
       <c r="O30" s="3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
       <c r="R30" s="3">
-        <v>40400</v>
-      </c>
-      <c r="S30" s="3"/>
+        <v>30982</v>
+      </c>
+      <c r="S30" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
@@ -3241,19 +3339,21 @@
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
       <c r="Z30" s="6" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="AA30" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB30" s="3"/>
+      <c r="AB30" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:28">
       <c r="A31" s="7">
         <v>29</v>
       </c>
       <c r="B31" s="7">
-        <v>2026100417</v>
+        <v>2026100085</v>
       </c>
       <c r="C31" s="7">
         <v>1</v>
@@ -3262,46 +3362,44 @@
         <v>29</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>63</v>
+        <v>153</v>
       </c>
       <c r="K31" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L31" s="8" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="N31" s="8" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="O31" s="7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
       <c r="R31" s="7">
-        <v>155867</v>
-      </c>
-      <c r="S31" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>30982</v>
+      </c>
+      <c r="S31" s="7"/>
       <c r="T31" s="7"/>
       <c r="U31" s="7"/>
       <c r="V31" s="7"/>
@@ -3309,9 +3407,11 @@
       <c r="X31" s="7"/>
       <c r="Y31" s="7"/>
       <c r="Z31" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA31" s="7"/>
+        <v>138</v>
+      </c>
+      <c r="AA31" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="AB31" s="7"/>
     </row>
     <row r="32" spans="1:28">
@@ -3319,7 +3419,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="3">
-        <v>2026100418</v>
+        <v>2026100071</v>
       </c>
       <c r="C32" s="3">
         <v>1</v>
@@ -3328,19 +3428,19 @@
         <v>29</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>145</v>
+        <v>86</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>63</v>
@@ -3349,23 +3449,23 @@
         <v>36</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="N32" s="6" t="s">
-        <v>150</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N32" s="6"/>
       <c r="O32" s="3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
       <c r="R32" s="3">
-        <v>155867</v>
-      </c>
-      <c r="S32" s="3"/>
+        <v>40400</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
@@ -3373,17 +3473,21 @@
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
       <c r="Z32" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA32" s="3"/>
-      <c r="AB32" s="3"/>
+        <v>138</v>
+      </c>
+      <c r="AA32" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="33" spans="1:28">
       <c r="A33" s="7">
         <v>31</v>
       </c>
       <c r="B33" s="7">
-        <v>2026100415</v>
+        <v>2026100072</v>
       </c>
       <c r="C33" s="7">
         <v>1</v>
@@ -3392,19 +3496,19 @@
         <v>29</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>151</v>
+        <v>86</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="J33" s="7" t="s">
         <v>63</v>
@@ -3413,25 +3517,21 @@
         <v>36</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="N33" s="8" t="s">
-        <v>150</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N33" s="8"/>
       <c r="O33" s="7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="P33" s="7"/>
       <c r="Q33" s="7"/>
       <c r="R33" s="7">
-        <v>16305</v>
-      </c>
-      <c r="S33" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>40400</v>
+      </c>
+      <c r="S33" s="7"/>
       <c r="T33" s="7"/>
       <c r="U33" s="7"/>
       <c r="V33" s="7"/>
@@ -3439,9 +3539,11 @@
       <c r="X33" s="7"/>
       <c r="Y33" s="7"/>
       <c r="Z33" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA33" s="7"/>
+        <v>138</v>
+      </c>
+      <c r="AA33" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="AB33" s="7"/>
     </row>
     <row r="34" spans="1:28">
@@ -3449,7 +3551,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="3">
-        <v>2026100416</v>
+        <v>2026100417</v>
       </c>
       <c r="C34" s="3">
         <v>1</v>
@@ -3458,19 +3560,19 @@
         <v>29</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="J34" s="3" t="s">
         <v>63</v>
@@ -3479,23 +3581,25 @@
         <v>36</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
       <c r="R34" s="3">
-        <v>16305</v>
-      </c>
-      <c r="S34" s="3"/>
+        <v>155867</v>
+      </c>
+      <c r="S34" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
@@ -3503,7 +3607,7 @@
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
       <c r="Z34" s="6" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="AA34" s="3"/>
       <c r="AB34" s="3"/>
@@ -3513,7 +3617,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="7">
-        <v>2026100081</v>
+        <v>2026100418</v>
       </c>
       <c r="C35" s="7">
         <v>1</v>
@@ -3522,48 +3626,44 @@
         <v>29</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>97</v>
+        <v>161</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>156</v>
+        <v>63</v>
       </c>
       <c r="K35" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L35" s="8" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="N35" s="8" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="O35" s="7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="P35" s="7"/>
-      <c r="Q35" s="7">
-        <v>3224</v>
-      </c>
+      <c r="Q35" s="7"/>
       <c r="R35" s="7">
-        <v>435290</v>
-      </c>
-      <c r="S35" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>155867</v>
+      </c>
+      <c r="S35" s="7"/>
       <c r="T35" s="7"/>
       <c r="U35" s="7"/>
       <c r="V35" s="7"/>
@@ -3571,21 +3671,17 @@
       <c r="X35" s="7"/>
       <c r="Y35" s="7"/>
       <c r="Z35" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA35" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB35" s="7">
-        <v>1</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AA35" s="7"/>
+      <c r="AB35" s="7"/>
     </row>
     <row r="36" spans="1:28">
       <c r="A36" s="3">
         <v>34</v>
       </c>
       <c r="B36" s="3">
-        <v>2026100082</v>
+        <v>2026100415</v>
       </c>
       <c r="C36" s="3">
         <v>1</v>
@@ -3594,46 +3690,46 @@
         <v>29</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>156</v>
+        <v>63</v>
       </c>
       <c r="K36" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="P36" s="3"/>
-      <c r="Q36" s="3">
-        <v>3224</v>
-      </c>
+      <c r="Q36" s="3"/>
       <c r="R36" s="3">
-        <v>435290</v>
-      </c>
-      <c r="S36" s="3"/>
+        <v>16305</v>
+      </c>
+      <c r="S36" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T36" s="3"/>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
@@ -3641,11 +3737,9 @@
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
       <c r="Z36" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA36" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AA36" s="3"/>
       <c r="AB36" s="3"/>
     </row>
     <row r="37" spans="1:28">
@@ -3653,7 +3747,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="7">
-        <v>2026100452</v>
+        <v>2026100416</v>
       </c>
       <c r="C37" s="7">
         <v>1</v>
@@ -3662,48 +3756,44 @@
         <v>29</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>101</v>
+        <v>168</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>161</v>
+        <v>63</v>
       </c>
       <c r="K37" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M37" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N37" s="8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O37" s="7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="P37" s="7"/>
-      <c r="Q37" s="7">
-        <v>8413</v>
-      </c>
+      <c r="Q37" s="7"/>
       <c r="R37" s="7">
-        <v>43234</v>
-      </c>
-      <c r="S37" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>16305</v>
+      </c>
+      <c r="S37" s="7"/>
       <c r="T37" s="7"/>
       <c r="U37" s="7"/>
       <c r="V37" s="7"/>
@@ -3711,7 +3801,7 @@
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
       <c r="Z37" s="8" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="AA37" s="7"/>
       <c r="AB37" s="7"/>
@@ -3721,7 +3811,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="3">
-        <v>2026100453</v>
+        <v>2026100081</v>
       </c>
       <c r="C38" s="3">
         <v>1</v>
@@ -3730,46 +3820,48 @@
         <v>29</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>159</v>
+        <v>108</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>101</v>
+        <v>170</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="K38" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="P38" s="3"/>
       <c r="Q38" s="3">
-        <v>8413</v>
+        <v>3224</v>
       </c>
       <c r="R38" s="3">
-        <v>43234</v>
-      </c>
-      <c r="S38" s="3"/>
+        <v>435290</v>
+      </c>
+      <c r="S38" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
@@ -3777,17 +3869,21 @@
       <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
       <c r="Z38" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA38" s="3"/>
-      <c r="AB38" s="3"/>
+        <v>138</v>
+      </c>
+      <c r="AA38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB38" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="39" spans="1:28">
       <c r="A39" s="7">
         <v>37</v>
       </c>
       <c r="B39" s="7">
-        <v>2026100434</v>
+        <v>2026100082</v>
       </c>
       <c r="C39" s="7">
         <v>1</v>
@@ -3796,46 +3892,46 @@
         <v>29</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>165</v>
+        <v>108</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="K39" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>126</v>
+        <v>173</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="N39" s="8" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="O39" s="7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="P39" s="7"/>
-      <c r="Q39" s="7"/>
+      <c r="Q39" s="7">
+        <v>3224</v>
+      </c>
       <c r="R39" s="7">
-        <v>288497</v>
-      </c>
-      <c r="S39" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>435290</v>
+      </c>
+      <c r="S39" s="7"/>
       <c r="T39" s="7"/>
       <c r="U39" s="7"/>
       <c r="V39" s="7"/>
@@ -3843,9 +3939,11 @@
       <c r="X39" s="7"/>
       <c r="Y39" s="7"/>
       <c r="Z39" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA39" s="7"/>
+        <v>138</v>
+      </c>
+      <c r="AA39" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="AB39" s="7"/>
     </row>
     <row r="40" spans="1:28">
@@ -3853,7 +3951,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="3">
-        <v>2026100435</v>
+        <v>2026100524</v>
       </c>
       <c r="C40" s="3">
         <v>1</v>
@@ -3862,42 +3960,44 @@
         <v>29</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="K40" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>126</v>
+        <v>179</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="O40" s="3" t="s">
         <v>40</v>
       </c>
       <c r="P40" s="3"/>
-      <c r="Q40" s="3"/>
+      <c r="Q40" s="3">
+        <v>121</v>
+      </c>
       <c r="R40" s="3">
-        <v>288497</v>
+        <v>199</v>
       </c>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
@@ -3907,17 +4007,21 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA40" s="3"/>
-      <c r="AB40" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="AA40" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB40" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="41" spans="1:28">
       <c r="A41" s="7">
         <v>39</v>
       </c>
       <c r="B41" s="7">
-        <v>2026100408</v>
+        <v>2026100452</v>
       </c>
       <c r="C41" s="7">
         <v>1</v>
@@ -3926,46 +4030,44 @@
         <v>29</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>171</v>
+        <v>132</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>117</v>
+        <v>182</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>35</v>
+        <v>178</v>
       </c>
       <c r="K41" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L41" s="8" t="s">
-        <v>119</v>
+        <v>184</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="N41" s="8" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="O41" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="P41" s="7">
-        <v>2879</v>
-      </c>
+      <c r="P41" s="7"/>
       <c r="Q41" s="7">
-        <v>3812</v>
+        <v>8413</v>
       </c>
       <c r="R41" s="7">
-        <v>18568</v>
+        <v>43234</v>
       </c>
       <c r="S41" s="7" t="s">
         <v>41</v>
@@ -3977,21 +4079,17 @@
       <c r="X41" s="7"/>
       <c r="Y41" s="7"/>
       <c r="Z41" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA41" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB41" s="7">
-        <v>1</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AA41" s="7"/>
+      <c r="AB41" s="7"/>
     </row>
     <row r="42" spans="1:28">
       <c r="A42" s="3">
         <v>40</v>
       </c>
       <c r="B42" s="3">
-        <v>2026100409</v>
+        <v>2026100453</v>
       </c>
       <c r="C42" s="3">
         <v>1</v>
@@ -4000,46 +4098,44 @@
         <v>29</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>171</v>
+        <v>132</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>117</v>
+        <v>182</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>35</v>
+        <v>178</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>119</v>
+        <v>184</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="P42" s="3">
-        <v>2879</v>
-      </c>
+      <c r="P42" s="3"/>
       <c r="Q42" s="3">
-        <v>3812</v>
+        <v>8413</v>
       </c>
       <c r="R42" s="3">
-        <v>18568</v>
+        <v>43234</v>
       </c>
       <c r="S42" s="3"/>
       <c r="T42" s="3"/>
@@ -4049,11 +4145,9 @@
       <c r="X42" s="3"/>
       <c r="Y42" s="3"/>
       <c r="Z42" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA42" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AA42" s="3"/>
       <c r="AB42" s="3"/>
     </row>
     <row r="43" spans="1:28">
@@ -4061,7 +4155,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="7">
-        <v>2026100406</v>
+        <v>2026100434</v>
       </c>
       <c r="C43" s="7">
         <v>1</v>
@@ -4070,46 +4164,42 @@
         <v>29</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>171</v>
+        <v>132</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>91</v>
+        <v>187</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>117</v>
+        <v>188</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>35</v>
+        <v>190</v>
       </c>
       <c r="K43" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L43" s="8" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="N43" s="8" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="O43" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="P43" s="7">
-        <v>1100</v>
-      </c>
-      <c r="Q43" s="7">
-        <v>2214</v>
-      </c>
+      <c r="P43" s="7"/>
+      <c r="Q43" s="7"/>
       <c r="R43" s="7">
-        <v>14049</v>
+        <v>288497</v>
       </c>
       <c r="S43" s="7" t="s">
         <v>41</v>
@@ -4121,21 +4211,17 @@
       <c r="X43" s="7"/>
       <c r="Y43" s="7"/>
       <c r="Z43" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA43" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB43" s="7">
-        <v>1</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AA43" s="7"/>
+      <c r="AB43" s="7"/>
     </row>
     <row r="44" spans="1:28">
       <c r="A44" s="3">
         <v>42</v>
       </c>
       <c r="B44" s="3">
-        <v>2026100407</v>
+        <v>2026100435</v>
       </c>
       <c r="C44" s="3">
         <v>1</v>
@@ -4144,46 +4230,42 @@
         <v>29</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>171</v>
+        <v>132</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>91</v>
+        <v>187</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>117</v>
+        <v>188</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>35</v>
+        <v>190</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="P44" s="3">
-        <v>1100</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>2214</v>
-      </c>
+      <c r="P44" s="3"/>
+      <c r="Q44" s="3"/>
       <c r="R44" s="3">
-        <v>14049</v>
+        <v>288497</v>
       </c>
       <c r="S44" s="3"/>
       <c r="T44" s="3"/>
@@ -4193,11 +4275,9 @@
       <c r="X44" s="3"/>
       <c r="Y44" s="3"/>
       <c r="Z44" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA44" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AA44" s="3"/>
       <c r="AB44" s="3"/>
     </row>
     <row r="45" spans="1:28">
@@ -4205,7 +4285,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="7">
-        <v>2026100264</v>
+        <v>2026100408</v>
       </c>
       <c r="C45" s="7">
         <v>1</v>
@@ -4214,19 +4294,19 @@
         <v>29</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>178</v>
+        <v>133</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>32</v>
+        <v>167</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="J45" s="7" t="s">
         <v>35</v>
@@ -4235,23 +4315,25 @@
         <v>36</v>
       </c>
       <c r="L45" s="8" t="s">
-        <v>37</v>
+        <v>135</v>
       </c>
       <c r="M45" s="8" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="N45" s="8" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="O45" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="P45" s="7"/>
+      <c r="P45" s="7">
+        <v>2879</v>
+      </c>
       <c r="Q45" s="7">
-        <v>843</v>
+        <v>3812</v>
       </c>
       <c r="R45" s="7">
-        <v>7289</v>
+        <v>18568</v>
       </c>
       <c r="S45" s="7" t="s">
         <v>41</v>
@@ -4265,15 +4347,19 @@
       <c r="Z45" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="AA45" s="7"/>
-      <c r="AB45" s="7"/>
+      <c r="AA45" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB45" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="46" spans="1:28">
       <c r="A46" s="3">
         <v>44</v>
       </c>
       <c r="B46" s="3">
-        <v>2026100265</v>
+        <v>2026100409</v>
       </c>
       <c r="C46" s="3">
         <v>1</v>
@@ -4282,19 +4368,19 @@
         <v>29</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>178</v>
+        <v>133</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>32</v>
+        <v>167</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>35</v>
@@ -4303,23 +4389,25 @@
         <v>36</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>37</v>
+        <v>135</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="P46" s="3"/>
+      <c r="P46" s="3">
+        <v>2879</v>
+      </c>
       <c r="Q46" s="3">
-        <v>843</v>
+        <v>3812</v>
       </c>
       <c r="R46" s="3">
-        <v>7289</v>
+        <v>18568</v>
       </c>
       <c r="S46" s="3"/>
       <c r="T46" s="3"/>
@@ -4341,7 +4429,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="7">
-        <v>2026100402</v>
+        <v>2026100407</v>
       </c>
       <c r="C47" s="7">
         <v>1</v>
@@ -4350,46 +4438,48 @@
         <v>29</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>182</v>
+        <v>102</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>183</v>
+        <v>133</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="K47" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L47" s="8" t="s">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="M47" s="8" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="N47" s="8" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="O47" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="P47" s="7"/>
-      <c r="Q47" s="7"/>
+        <v>40</v>
+      </c>
+      <c r="P47" s="7">
+        <v>1100</v>
+      </c>
+      <c r="Q47" s="7">
+        <v>2214</v>
+      </c>
       <c r="R47" s="7">
-        <v>211147</v>
-      </c>
-      <c r="S47" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>14049</v>
+      </c>
+      <c r="S47" s="7"/>
       <c r="T47" s="7"/>
       <c r="U47" s="7"/>
       <c r="V47" s="7"/>
@@ -4411,7 +4501,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="3">
-        <v>2026100403</v>
+        <v>2026100406</v>
       </c>
       <c r="C48" s="3">
         <v>1</v>
@@ -4420,44 +4510,50 @@
         <v>29</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>182</v>
+        <v>102</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>183</v>
+        <v>133</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P48" s="3"/>
-      <c r="Q48" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="P48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>2214</v>
+      </c>
       <c r="R48" s="3">
-        <v>211147</v>
-      </c>
-      <c r="S48" s="3"/>
+        <v>14049</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
@@ -4477,7 +4573,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="7">
-        <v>2026100404</v>
+        <v>2026100264</v>
       </c>
       <c r="C49" s="7">
         <v>1</v>
@@ -4486,42 +4582,44 @@
         <v>29</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>91</v>
+        <v>32</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="K49" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L49" s="8" t="s">
-        <v>185</v>
+        <v>37</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="N49" s="8" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="O49" s="7" t="s">
         <v>48</v>
       </c>
       <c r="P49" s="7"/>
-      <c r="Q49" s="7"/>
+      <c r="Q49" s="7">
+        <v>843</v>
+      </c>
       <c r="R49" s="7">
-        <v>232657</v>
+        <v>7289</v>
       </c>
       <c r="S49" s="7" t="s">
         <v>41</v>
@@ -4535,19 +4633,15 @@
       <c r="Z49" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="AA49" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB49" s="7">
-        <v>1</v>
-      </c>
+      <c r="AA49" s="7"/>
+      <c r="AB49" s="7"/>
     </row>
     <row r="50" spans="1:28">
       <c r="A50" s="3">
         <v>48</v>
       </c>
       <c r="B50" s="3">
-        <v>2026100405</v>
+        <v>2026100265</v>
       </c>
       <c r="C50" s="3">
         <v>1</v>
@@ -4556,42 +4650,44 @@
         <v>29</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>91</v>
+        <v>32</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="K50" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>185</v>
+        <v>37</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="O50" s="3" t="s">
         <v>40</v>
       </c>
       <c r="P50" s="3"/>
-      <c r="Q50" s="3"/>
+      <c r="Q50" s="3">
+        <v>843</v>
+      </c>
       <c r="R50" s="3">
-        <v>232657</v>
+        <v>7289</v>
       </c>
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
@@ -4613,7 +4709,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="7">
-        <v>2026100429</v>
+        <v>2026100533</v>
       </c>
       <c r="C51" s="7">
         <v>1</v>
@@ -4622,44 +4718,46 @@
         <v>29</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>191</v>
+        <v>97</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>75</v>
+        <v>204</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>63</v>
+        <v>153</v>
       </c>
       <c r="K51" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L51" s="8" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="M51" s="8" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="N51" s="8" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="O51" s="7" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="P51" s="7"/>
       <c r="Q51" s="7"/>
       <c r="R51" s="7">
-        <v>66361</v>
-      </c>
-      <c r="S51" s="7"/>
+        <v>586</v>
+      </c>
+      <c r="S51" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T51" s="7"/>
       <c r="U51" s="7"/>
       <c r="V51" s="7"/>
@@ -4669,19 +4767,15 @@
       <c r="Z51" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="AA51" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB51" s="7">
-        <v>1</v>
-      </c>
+      <c r="AA51" s="7"/>
+      <c r="AB51" s="7"/>
     </row>
     <row r="52" spans="1:28">
       <c r="A52" s="3">
         <v>50</v>
       </c>
       <c r="B52" s="3">
-        <v>2026100428</v>
+        <v>2026100534</v>
       </c>
       <c r="C52" s="3">
         <v>1</v>
@@ -4690,46 +4784,44 @@
         <v>29</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>191</v>
+        <v>97</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>75</v>
+        <v>204</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>63</v>
+        <v>153</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="P52" s="3"/>
       <c r="Q52" s="3"/>
       <c r="R52" s="3">
-        <v>66361</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>586</v>
+      </c>
+      <c r="S52" s="3"/>
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
@@ -4739,7 +4831,9 @@
       <c r="Z52" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AA52" s="3"/>
+      <c r="AA52" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="AB52" s="3"/>
     </row>
     <row r="53" spans="1:28">
@@ -4747,7 +4841,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="7">
-        <v>2026100430</v>
+        <v>2026100403</v>
       </c>
       <c r="C53" s="7">
         <v>1</v>
@@ -4756,48 +4850,44 @@
         <v>29</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>156</v>
+        <v>63</v>
       </c>
       <c r="K53" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L53" s="8" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="N53" s="8" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="O53" s="7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="P53" s="7"/>
-      <c r="Q53" s="7">
-        <v>705</v>
-      </c>
+      <c r="Q53" s="7"/>
       <c r="R53" s="7">
-        <v>46011</v>
-      </c>
-      <c r="S53" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>211147</v>
+      </c>
+      <c r="S53" s="7"/>
       <c r="T53" s="7"/>
       <c r="U53" s="7"/>
       <c r="V53" s="7"/>
@@ -4807,15 +4897,19 @@
       <c r="Z53" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="AA53" s="7"/>
-      <c r="AB53" s="7"/>
+      <c r="AA53" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB53" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="54" spans="1:28">
       <c r="A54" s="3">
         <v>52</v>
       </c>
       <c r="B54" s="3">
-        <v>2026100431</v>
+        <v>2026100402</v>
       </c>
       <c r="C54" s="3">
         <v>1</v>
@@ -4824,46 +4918,46 @@
         <v>29</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>156</v>
+        <v>63</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="O54" s="3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="P54" s="3"/>
-      <c r="Q54" s="3">
-        <v>705</v>
-      </c>
+      <c r="Q54" s="3"/>
       <c r="R54" s="3">
-        <v>46011</v>
-      </c>
-      <c r="S54" s="3"/>
+        <v>211147</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
@@ -4883,7 +4977,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="7">
-        <v>2026100035</v>
+        <v>2026100404</v>
       </c>
       <c r="C55" s="7">
         <v>1</v>
@@ -4892,34 +4986,34 @@
         <v>29</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>183</v>
+        <v>102</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>201</v>
+        <v>63</v>
       </c>
       <c r="K55" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L55" s="8" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="N55" s="8" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="O55" s="7" t="s">
         <v>48</v>
@@ -4927,7 +5021,7 @@
       <c r="P55" s="7"/>
       <c r="Q55" s="7"/>
       <c r="R55" s="7">
-        <v>125248</v>
+        <v>232657</v>
       </c>
       <c r="S55" s="7" t="s">
         <v>41</v>
@@ -4941,15 +5035,19 @@
       <c r="Z55" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="AA55" s="7"/>
-      <c r="AB55" s="7"/>
+      <c r="AA55" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB55" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" spans="1:28">
       <c r="A56" s="3">
         <v>54</v>
       </c>
       <c r="B56" s="3">
-        <v>2026100036</v>
+        <v>2026100405</v>
       </c>
       <c r="C56" s="3">
         <v>1</v>
@@ -4958,34 +5056,34 @@
         <v>29</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>183</v>
+        <v>102</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>201</v>
+        <v>63</v>
       </c>
       <c r="K56" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="O56" s="3" t="s">
         <v>40</v>
@@ -4993,7 +5091,7 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3">
-        <v>125248</v>
+        <v>232657</v>
       </c>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
@@ -5015,7 +5113,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="7">
-        <v>2026100037</v>
+        <v>2026100428</v>
       </c>
       <c r="C57" s="7">
         <v>1</v>
@@ -5024,44 +5122,46 @@
         <v>29</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>183</v>
+        <v>218</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>201</v>
+        <v>63</v>
       </c>
       <c r="K57" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L57" s="8" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="M57" s="8" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="N57" s="8" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="O57" s="7" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="P57" s="7"/>
       <c r="Q57" s="7"/>
       <c r="R57" s="7">
-        <v>125248</v>
-      </c>
-      <c r="S57" s="7"/>
+        <v>66361</v>
+      </c>
+      <c r="S57" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T57" s="7"/>
       <c r="U57" s="7"/>
       <c r="V57" s="7"/>
@@ -5069,11 +5169,9 @@
       <c r="X57" s="7"/>
       <c r="Y57" s="7"/>
       <c r="Z57" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA57" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="AA57" s="7"/>
       <c r="AB57" s="7"/>
     </row>
     <row r="58" spans="1:28">
@@ -5081,7 +5179,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="3">
-        <v>2026100098</v>
+        <v>2026100429</v>
       </c>
       <c r="C58" s="3">
         <v>1</v>
@@ -5090,46 +5188,44 @@
         <v>29</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>207</v>
+        <v>86</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>209</v>
+        <v>63</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="P58" s="3"/>
       <c r="Q58" s="3"/>
       <c r="R58" s="3">
-        <v>60189</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>66361</v>
+      </c>
+      <c r="S58" s="3"/>
       <c r="T58" s="3"/>
       <c r="U58" s="3"/>
       <c r="V58" s="3"/>
@@ -5139,7 +5235,9 @@
       <c r="Z58" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AA58" s="3"/>
+      <c r="AA58" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="AB58" s="3"/>
     </row>
     <row r="59" spans="1:28">
@@ -5147,7 +5245,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="7">
-        <v>2026100099</v>
+        <v>2026100430</v>
       </c>
       <c r="C59" s="7">
         <v>1</v>
@@ -5156,44 +5254,48 @@
         <v>29</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>206</v>
+        <v>86</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="I59" s="7" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="K59" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L59" s="8" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="M59" s="8" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="N59" s="8" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="O59" s="7" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="P59" s="7"/>
-      <c r="Q59" s="7"/>
+      <c r="Q59" s="7">
+        <v>705</v>
+      </c>
       <c r="R59" s="7">
-        <v>60189</v>
-      </c>
-      <c r="S59" s="7"/>
+        <v>46011</v>
+      </c>
+      <c r="S59" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T59" s="7"/>
       <c r="U59" s="7"/>
       <c r="V59" s="7"/>
@@ -5203,9 +5305,7 @@
       <c r="Z59" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="AA59" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="AA59" s="7"/>
       <c r="AB59" s="7"/>
     </row>
     <row r="60" spans="1:28">
@@ -5213,7 +5313,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="3">
-        <v>2026100090</v>
+        <v>2026100431</v>
       </c>
       <c r="C60" s="3">
         <v>1</v>
@@ -5222,46 +5322,46 @@
         <v>29</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="P60" s="3"/>
-      <c r="Q60" s="3"/>
+      <c r="Q60" s="3">
+        <v>705</v>
+      </c>
       <c r="R60" s="3">
-        <v>38975</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>46011</v>
+      </c>
+      <c r="S60" s="3"/>
       <c r="T60" s="3"/>
       <c r="U60" s="3"/>
       <c r="V60" s="3"/>
@@ -5271,7 +5371,9 @@
       <c r="Z60" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AA60" s="3"/>
+      <c r="AA60" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="AB60" s="3"/>
     </row>
     <row r="61" spans="1:28">
@@ -5279,7 +5381,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="7">
-        <v>2026100091</v>
+        <v>2026100035</v>
       </c>
       <c r="C61" s="7">
         <v>1</v>
@@ -5288,44 +5390,46 @@
         <v>29</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F61" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>50</v>
+        <v>209</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="I61" s="7" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="K61" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L61" s="8" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="M61" s="8" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="N61" s="8" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="O61" s="7" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="P61" s="7"/>
       <c r="Q61" s="7"/>
       <c r="R61" s="7">
-        <v>38975</v>
-      </c>
-      <c r="S61" s="7"/>
+        <v>125248</v>
+      </c>
+      <c r="S61" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T61" s="7"/>
       <c r="U61" s="7"/>
       <c r="V61" s="7"/>
@@ -5335,9 +5439,7 @@
       <c r="Z61" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="AA61" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="AA61" s="7"/>
       <c r="AB61" s="7"/>
     </row>
     <row r="62" spans="1:28">
@@ -5345,7 +5447,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="3">
-        <v>2026100086</v>
+        <v>2026100036</v>
       </c>
       <c r="C62" s="3">
         <v>1</v>
@@ -5354,42 +5456,42 @@
         <v>29</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>151</v>
+        <v>209</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="P62" s="3"/>
       <c r="Q62" s="3"/>
       <c r="R62" s="3">
-        <v>142212</v>
+        <v>125248</v>
       </c>
       <c r="S62" s="3"/>
       <c r="T62" s="3"/>
@@ -5399,21 +5501,19 @@
       <c r="X62" s="3"/>
       <c r="Y62" s="3"/>
       <c r="Z62" s="6" t="s">
-        <v>220</v>
+        <v>49</v>
       </c>
       <c r="AA62" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB62" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB62" s="3"/>
     </row>
     <row r="63" spans="1:28">
       <c r="A63" s="7">
         <v>61</v>
       </c>
       <c r="B63" s="7">
-        <v>2026100088</v>
+        <v>2026100037</v>
       </c>
       <c r="C63" s="7">
         <v>1</v>
@@ -5422,42 +5522,42 @@
         <v>29</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F63" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>111</v>
+        <v>210</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="I63" s="7" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="K63" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L63" s="8" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="M63" s="8" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="N63" s="8" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="O63" s="7" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="P63" s="7"/>
       <c r="Q63" s="7"/>
       <c r="R63" s="7">
-        <v>142212</v>
+        <v>125248</v>
       </c>
       <c r="S63" s="7"/>
       <c r="T63" s="7"/>
@@ -5467,21 +5567,19 @@
       <c r="X63" s="7"/>
       <c r="Y63" s="7"/>
       <c r="Z63" s="8" t="s">
-        <v>49</v>
+        <v>231</v>
       </c>
       <c r="AA63" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB63" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB63" s="7"/>
     </row>
     <row r="64" spans="1:28">
       <c r="A64" s="3">
         <v>62</v>
       </c>
       <c r="B64" s="3">
-        <v>2026100087</v>
+        <v>2026100697</v>
       </c>
       <c r="C64" s="3">
         <v>1</v>
@@ -5490,46 +5588,42 @@
         <v>29</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>111</v>
+        <v>232</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>50</v>
+        <v>233</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="K64" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="N64" s="6" t="s">
-        <v>219</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N64" s="6"/>
       <c r="O64" s="3" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="P64" s="3"/>
       <c r="Q64" s="3"/>
       <c r="R64" s="3">
-        <v>142212</v>
-      </c>
-      <c r="S64" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>181940</v>
+      </c>
+      <c r="S64" s="3"/>
       <c r="T64" s="3"/>
       <c r="U64" s="3"/>
       <c r="V64" s="3"/>
@@ -5537,17 +5631,21 @@
       <c r="X64" s="3"/>
       <c r="Y64" s="3"/>
       <c r="Z64" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA64" s="3"/>
-      <c r="AB64" s="3"/>
+        <v>237</v>
+      </c>
+      <c r="AA64" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB64" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="65" spans="1:28">
       <c r="A65" s="7">
         <v>63</v>
       </c>
       <c r="B65" s="7">
-        <v>2026100040</v>
+        <v>2026100699</v>
       </c>
       <c r="C65" s="7">
         <v>1</v>
@@ -5556,42 +5654,40 @@
         <v>29</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>91</v>
+        <v>233</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>117</v>
+        <v>238</v>
       </c>
       <c r="I65" s="7" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="K65" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L65" s="8" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="M65" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="N65" s="8" t="s">
-        <v>223</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N65" s="8"/>
       <c r="O65" s="7" t="s">
         <v>48</v>
       </c>
       <c r="P65" s="7"/>
       <c r="Q65" s="7"/>
       <c r="R65" s="7">
-        <v>310255</v>
+        <v>181940</v>
       </c>
       <c r="S65" s="7" t="s">
         <v>41</v>
@@ -5603,17 +5699,21 @@
       <c r="X65" s="7"/>
       <c r="Y65" s="7"/>
       <c r="Z65" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA65" s="7"/>
-      <c r="AB65" s="7"/>
+        <v>239</v>
+      </c>
+      <c r="AA65" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB65" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="66" spans="1:28">
       <c r="A66" s="3">
         <v>64</v>
       </c>
       <c r="B66" s="3">
-        <v>2026100041</v>
+        <v>2026100700</v>
       </c>
       <c r="C66" s="3">
         <v>1</v>
@@ -5622,42 +5722,40 @@
         <v>29</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>91</v>
+        <v>233</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>117</v>
+        <v>238</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="N66" s="6" t="s">
-        <v>223</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N66" s="6"/>
       <c r="O66" s="3" t="s">
         <v>40</v>
       </c>
       <c r="P66" s="3"/>
       <c r="Q66" s="3"/>
       <c r="R66" s="3">
-        <v>310255</v>
+        <v>181940</v>
       </c>
       <c r="S66" s="3"/>
       <c r="T66" s="3"/>
@@ -5667,7 +5765,7 @@
       <c r="X66" s="3"/>
       <c r="Y66" s="3"/>
       <c r="Z66" s="6" t="s">
-        <v>49</v>
+        <v>239</v>
       </c>
       <c r="AA66" s="3" t="s">
         <v>41</v>
@@ -5679,7 +5777,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="7">
-        <v>2026100066</v>
+        <v>2026100472</v>
       </c>
       <c r="C67" s="7">
         <v>1</v>
@@ -5688,42 +5786,44 @@
         <v>29</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>117</v>
+        <v>50</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>151</v>
+        <v>240</v>
       </c>
       <c r="I67" s="7" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>209</v>
+        <v>178</v>
       </c>
       <c r="K67" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L67" s="8" t="s">
-        <v>202</v>
+        <v>242</v>
       </c>
       <c r="M67" s="8" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="N67" s="8" t="s">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="O67" s="7" t="s">
         <v>48</v>
       </c>
       <c r="P67" s="7"/>
-      <c r="Q67" s="7"/>
+      <c r="Q67" s="7">
+        <v>9455</v>
+      </c>
       <c r="R67" s="7">
-        <v>233316</v>
+        <v>16868</v>
       </c>
       <c r="S67" s="7" t="s">
         <v>41</v>
@@ -5745,7 +5845,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="3">
-        <v>2026100067</v>
+        <v>2026100473</v>
       </c>
       <c r="C68" s="3">
         <v>1</v>
@@ -5754,42 +5854,44 @@
         <v>29</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>117</v>
+        <v>50</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>151</v>
+        <v>240</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>209</v>
+        <v>178</v>
       </c>
       <c r="K68" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>202</v>
+        <v>242</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="O68" s="3" t="s">
         <v>40</v>
       </c>
       <c r="P68" s="3"/>
-      <c r="Q68" s="3"/>
+      <c r="Q68" s="3">
+        <v>9455</v>
+      </c>
       <c r="R68" s="3">
-        <v>233316</v>
+        <v>16868</v>
       </c>
       <c r="S68" s="3"/>
       <c r="T68" s="3"/>
@@ -5811,7 +5913,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="7">
-        <v>2026100426</v>
+        <v>2026100098</v>
       </c>
       <c r="C69" s="7">
         <v>1</v>
@@ -5820,34 +5922,34 @@
         <v>29</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>151</v>
+        <v>240</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>191</v>
+        <v>244</v>
       </c>
       <c r="I69" s="7" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>168</v>
+        <v>71</v>
       </c>
       <c r="K69" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L69" s="8" t="s">
-        <v>193</v>
+        <v>246</v>
       </c>
       <c r="M69" s="8" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="N69" s="8" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="O69" s="7" t="s">
         <v>48</v>
@@ -5855,7 +5957,7 @@
       <c r="P69" s="7"/>
       <c r="Q69" s="7"/>
       <c r="R69" s="7">
-        <v>54727</v>
+        <v>60189</v>
       </c>
       <c r="S69" s="7" t="s">
         <v>41</v>
@@ -5877,7 +5979,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="3">
-        <v>2026100427</v>
+        <v>2026100099</v>
       </c>
       <c r="C70" s="3">
         <v>1</v>
@@ -5886,34 +5988,34 @@
         <v>29</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>151</v>
+        <v>240</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>191</v>
+        <v>244</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>168</v>
+        <v>71</v>
       </c>
       <c r="K70" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>193</v>
+        <v>246</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="O70" s="3" t="s">
         <v>40</v>
@@ -5921,7 +6023,7 @@
       <c r="P70" s="3"/>
       <c r="Q70" s="3"/>
       <c r="R70" s="3">
-        <v>54727</v>
+        <v>60189</v>
       </c>
       <c r="S70" s="3"/>
       <c r="T70" s="3"/>
@@ -5943,7 +6045,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="7">
-        <v>2026100432</v>
+        <v>2026100090</v>
       </c>
       <c r="C71" s="7">
         <v>1</v>
@@ -5952,34 +6054,34 @@
         <v>29</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>196</v>
+        <v>50</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>165</v>
+        <v>240</v>
       </c>
       <c r="I71" s="7" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>168</v>
+        <v>71</v>
       </c>
       <c r="K71" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L71" s="8" t="s">
-        <v>193</v>
+        <v>228</v>
       </c>
       <c r="M71" s="8" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="N71" s="8" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="O71" s="7" t="s">
         <v>48</v>
@@ -5987,7 +6089,7 @@
       <c r="P71" s="7"/>
       <c r="Q71" s="7"/>
       <c r="R71" s="7">
-        <v>545581</v>
+        <v>38975</v>
       </c>
       <c r="S71" s="7" t="s">
         <v>41</v>
@@ -6009,7 +6111,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="3">
-        <v>2026100433</v>
+        <v>2026100091</v>
       </c>
       <c r="C72" s="3">
         <v>1</v>
@@ -6018,34 +6120,34 @@
         <v>29</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>196</v>
+        <v>50</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>165</v>
+        <v>240</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>168</v>
+        <v>71</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>193</v>
+        <v>228</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>40</v>
@@ -6053,7 +6155,7 @@
       <c r="P72" s="3"/>
       <c r="Q72" s="3"/>
       <c r="R72" s="3">
-        <v>545581</v>
+        <v>38975</v>
       </c>
       <c r="S72" s="3"/>
       <c r="T72" s="3"/>
@@ -6075,7 +6177,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="7">
-        <v>2026100250</v>
+        <v>2026100086</v>
       </c>
       <c r="C73" s="7">
         <v>1</v>
@@ -6084,42 +6186,42 @@
         <v>29</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F73" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>207</v>
+        <v>167</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="I73" s="7" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>168</v>
+        <v>71</v>
       </c>
       <c r="K73" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L73" s="8" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="M73" s="8" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="N73" s="8" t="s">
-        <v>190</v>
+        <v>255</v>
       </c>
       <c r="O73" s="7" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="P73" s="7"/>
       <c r="Q73" s="7"/>
       <c r="R73" s="7">
-        <v>198369</v>
+        <v>142212</v>
       </c>
       <c r="S73" s="7"/>
       <c r="T73" s="7"/>
@@ -6129,7 +6231,7 @@
       <c r="X73" s="7"/>
       <c r="Y73" s="7"/>
       <c r="Z73" s="8" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="AA73" s="7" t="s">
         <v>41</v>
@@ -6143,7 +6245,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="3">
-        <v>2026100260</v>
+        <v>2026100087</v>
       </c>
       <c r="C74" s="3">
         <v>1</v>
@@ -6152,44 +6254,46 @@
         <v>29</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>32</v>
+        <v>127</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>237</v>
+        <v>50</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>77</v>
+        <v>228</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="P74" s="3"/>
       <c r="Q74" s="3"/>
       <c r="R74" s="3">
-        <v>0</v>
-      </c>
-      <c r="S74" s="3"/>
+        <v>142212</v>
+      </c>
+      <c r="S74" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T74" s="3"/>
       <c r="U74" s="3"/>
       <c r="V74" s="3"/>
@@ -6197,21 +6301,17 @@
       <c r="X74" s="3"/>
       <c r="Y74" s="3"/>
       <c r="Z74" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="AA74" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB74" s="3">
-        <v>1</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="AA74" s="3"/>
+      <c r="AB74" s="3"/>
     </row>
     <row r="75" spans="1:28">
       <c r="A75" s="7">
         <v>73</v>
       </c>
       <c r="B75" s="7">
-        <v>2026100306</v>
+        <v>2026100088</v>
       </c>
       <c r="C75" s="7">
         <v>1</v>
@@ -6220,52 +6320,52 @@
         <v>29</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F75" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>237</v>
+        <v>127</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>242</v>
+        <v>50</v>
       </c>
       <c r="I75" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="J75" s="7"/>
-      <c r="K75" s="7"/>
+        <v>253</v>
+      </c>
+      <c r="J75" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="K75" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L75" s="8" t="s">
-        <v>77</v>
+        <v>228</v>
       </c>
       <c r="M75" s="8" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="N75" s="8" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="O75" s="7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="P75" s="7"/>
       <c r="Q75" s="7"/>
       <c r="R75" s="7">
-        <v>0</v>
-      </c>
-      <c r="S75" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>142212</v>
+      </c>
+      <c r="S75" s="7"/>
       <c r="T75" s="7"/>
       <c r="U75" s="7"/>
       <c r="V75" s="7"/>
       <c r="W75" s="7"/>
       <c r="X75" s="7"/>
-      <c r="Y75" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y75" s="7"/>
       <c r="Z75" s="8" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="AA75" s="7" t="s">
         <v>41</v>
@@ -6277,7 +6377,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="3">
-        <v>2026100449</v>
+        <v>2026100040</v>
       </c>
       <c r="C76" s="3">
         <v>1</v>
@@ -6286,30 +6386,34 @@
         <v>29</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>243</v>
+        <v>193</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>244</v>
+        <v>102</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="J76" s="3"/>
-      <c r="K76" s="3"/>
+        <v>257</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L76" s="6" t="s">
-        <v>77</v>
+        <v>228</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>48</v>
@@ -6317,7 +6421,7 @@
       <c r="P76" s="3"/>
       <c r="Q76" s="3"/>
       <c r="R76" s="3">
-        <v>0</v>
+        <v>310255</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>41</v>
@@ -6329,21 +6433,17 @@
       <c r="X76" s="3"/>
       <c r="Y76" s="3"/>
       <c r="Z76" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA76" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB76" s="3">
-        <v>1</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="AA76" s="3"/>
+      <c r="AB76" s="3"/>
     </row>
     <row r="77" spans="1:28">
       <c r="A77" s="7">
         <v>75</v>
       </c>
       <c r="B77" s="7">
-        <v>2026100044</v>
+        <v>2026100041</v>
       </c>
       <c r="C77" s="7">
         <v>1</v>
@@ -6352,42 +6452,42 @@
         <v>29</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>243</v>
+        <v>193</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>244</v>
+        <v>102</v>
       </c>
       <c r="H77" s="7" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="I77" s="7" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="K77" s="7" t="s">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="L77" s="8" t="s">
-        <v>77</v>
+        <v>228</v>
       </c>
       <c r="M77" s="8" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="N77" s="8" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="O77" s="7" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="P77" s="7"/>
       <c r="Q77" s="7"/>
       <c r="R77" s="7">
-        <v>0</v>
+        <v>310255</v>
       </c>
       <c r="S77" s="7"/>
       <c r="T77" s="7"/>
@@ -6397,7 +6497,7 @@
       <c r="X77" s="7"/>
       <c r="Y77" s="7"/>
       <c r="Z77" s="8" t="s">
-        <v>248</v>
+        <v>49</v>
       </c>
       <c r="AA77" s="7" t="s">
         <v>41</v>
@@ -6409,7 +6509,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="3">
-        <v>2026100047</v>
+        <v>2026100066</v>
       </c>
       <c r="C78" s="3">
         <v>1</v>
@@ -6418,44 +6518,46 @@
         <v>29</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>243</v>
+        <v>193</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>244</v>
+        <v>133</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>77</v>
+        <v>228</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="O78" s="3" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="P78" s="3"/>
       <c r="Q78" s="3"/>
       <c r="R78" s="3">
-        <v>0</v>
-      </c>
-      <c r="S78" s="3"/>
+        <v>233316</v>
+      </c>
+      <c r="S78" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T78" s="3"/>
       <c r="U78" s="3"/>
       <c r="V78" s="3"/>
@@ -6463,45 +6565,773 @@
       <c r="X78" s="3"/>
       <c r="Y78" s="3"/>
       <c r="Z78" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="AA78" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="AA78" s="3"/>
       <c r="AB78" s="3"/>
     </row>
     <row r="79" spans="1:28">
-      <c r="A79" s="9"/>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="9"/>
-      <c r="H79" s="9"/>
-      <c r="I79" s="9"/>
-      <c r="J79" s="9"/>
-      <c r="K79" s="9"/>
-      <c r="L79" s="10"/>
-      <c r="M79" s="10"/>
-      <c r="N79" s="10"/>
-      <c r="O79" s="9"/>
-      <c r="P79" s="9"/>
-      <c r="Q79" s="9"/>
-      <c r="R79" s="9"/>
-      <c r="S79" s="9"/>
-      <c r="T79" s="9"/>
-      <c r="U79" s="9"/>
-      <c r="V79" s="9"/>
-      <c r="W79" s="9"/>
-      <c r="X79" s="9"/>
-      <c r="Y79" s="9"/>
-      <c r="Z79" s="10"/>
-      <c r="AA79" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="AB79" s="9">
-        <v>28</v>
+      <c r="A79" s="7">
+        <v>77</v>
+      </c>
+      <c r="B79" s="7">
+        <v>2026100067</v>
+      </c>
+      <c r="C79" s="7">
+        <v>1</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G79" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="H79" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="I79" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="J79" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="K79" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L79" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="M79" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="N79" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="O79" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P79" s="7"/>
+      <c r="Q79" s="7"/>
+      <c r="R79" s="7">
+        <v>233316</v>
+      </c>
+      <c r="S79" s="7"/>
+      <c r="T79" s="7"/>
+      <c r="U79" s="7"/>
+      <c r="V79" s="7"/>
+      <c r="W79" s="7"/>
+      <c r="X79" s="7"/>
+      <c r="Y79" s="7"/>
+      <c r="Z79" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA79" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB79" s="7"/>
+    </row>
+    <row r="80" spans="1:28">
+      <c r="A80" s="3">
+        <v>78</v>
+      </c>
+      <c r="B80" s="3">
+        <v>2026100426</v>
+      </c>
+      <c r="C80" s="3">
+        <v>1</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L80" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="M80" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="N80" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="O80" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P80" s="3"/>
+      <c r="Q80" s="3"/>
+      <c r="R80" s="3">
+        <v>54727</v>
+      </c>
+      <c r="S80" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T80" s="3"/>
+      <c r="U80" s="3"/>
+      <c r="V80" s="3"/>
+      <c r="W80" s="3"/>
+      <c r="X80" s="3"/>
+      <c r="Y80" s="3"/>
+      <c r="Z80" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA80" s="3"/>
+      <c r="AB80" s="3"/>
+    </row>
+    <row r="81" spans="1:28">
+      <c r="A81" s="7">
+        <v>79</v>
+      </c>
+      <c r="B81" s="7">
+        <v>2026100427</v>
+      </c>
+      <c r="C81" s="7">
+        <v>1</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G81" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="H81" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="I81" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="J81" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="K81" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L81" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="M81" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="N81" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="O81" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P81" s="7"/>
+      <c r="Q81" s="7"/>
+      <c r="R81" s="7">
+        <v>54727</v>
+      </c>
+      <c r="S81" s="7"/>
+      <c r="T81" s="7"/>
+      <c r="U81" s="7"/>
+      <c r="V81" s="7"/>
+      <c r="W81" s="7"/>
+      <c r="X81" s="7"/>
+      <c r="Y81" s="7"/>
+      <c r="Z81" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA81" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB81" s="7"/>
+    </row>
+    <row r="82" spans="1:28">
+      <c r="A82" s="3">
+        <v>80</v>
+      </c>
+      <c r="B82" s="3">
+        <v>2026100432</v>
+      </c>
+      <c r="C82" s="3">
+        <v>1</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L82" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="M82" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="N82" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="O82" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3">
+        <v>545581</v>
+      </c>
+      <c r="S82" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA82" s="3"/>
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="1:28">
+      <c r="A83" s="7">
+        <v>81</v>
+      </c>
+      <c r="B83" s="7">
+        <v>2026100433</v>
+      </c>
+      <c r="C83" s="7">
+        <v>1</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G83" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="H83" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="I83" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="J83" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="K83" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L83" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="M83" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="N83" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="O83" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P83" s="7"/>
+      <c r="Q83" s="7"/>
+      <c r="R83" s="7">
+        <v>545581</v>
+      </c>
+      <c r="S83" s="7"/>
+      <c r="T83" s="7"/>
+      <c r="U83" s="7"/>
+      <c r="V83" s="7"/>
+      <c r="W83" s="7"/>
+      <c r="X83" s="7"/>
+      <c r="Y83" s="7"/>
+      <c r="Z83" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA83" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB83" s="7"/>
+    </row>
+    <row r="84" spans="1:28">
+      <c r="A84" s="3">
+        <v>82</v>
+      </c>
+      <c r="B84" s="3">
+        <v>2026100250</v>
+      </c>
+      <c r="C84" s="3">
+        <v>1</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L84" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="M84" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="N84" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="O84" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="P84" s="3"/>
+      <c r="Q84" s="3"/>
+      <c r="R84" s="3">
+        <v>198369</v>
+      </c>
+      <c r="S84" s="3"/>
+      <c r="T84" s="3"/>
+      <c r="U84" s="3"/>
+      <c r="V84" s="3"/>
+      <c r="W84" s="3"/>
+      <c r="X84" s="3"/>
+      <c r="Y84" s="3"/>
+      <c r="Z84" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="AA84" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB84" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:28">
+      <c r="A85" s="7">
+        <v>83</v>
+      </c>
+      <c r="B85" s="7">
+        <v>2026100260</v>
+      </c>
+      <c r="C85" s="7">
+        <v>1</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G85" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H85" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="I85" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="J85" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K85" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="L85" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M85" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="N85" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="O85" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="P85" s="7"/>
+      <c r="Q85" s="7"/>
+      <c r="R85" s="7">
+        <v>0</v>
+      </c>
+      <c r="S85" s="7"/>
+      <c r="T85" s="7"/>
+      <c r="U85" s="7"/>
+      <c r="V85" s="7"/>
+      <c r="W85" s="7"/>
+      <c r="X85" s="7"/>
+      <c r="Y85" s="7"/>
+      <c r="Z85" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="AA85" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB85" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:28">
+      <c r="A86" s="3">
+        <v>84</v>
+      </c>
+      <c r="B86" s="3">
+        <v>2026100306</v>
+      </c>
+      <c r="C86" s="3">
+        <v>1</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="J86" s="3"/>
+      <c r="K86" s="3"/>
+      <c r="L86" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="M86" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="N86" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="O86" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P86" s="3"/>
+      <c r="Q86" s="3"/>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T86" s="3"/>
+      <c r="U86" s="3"/>
+      <c r="V86" s="3"/>
+      <c r="W86" s="3"/>
+      <c r="X86" s="3"/>
+      <c r="Y86" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z86" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA86" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB86" s="3"/>
+    </row>
+    <row r="87" spans="1:28">
+      <c r="A87" s="7">
+        <v>85</v>
+      </c>
+      <c r="B87" s="7">
+        <v>2026100044</v>
+      </c>
+      <c r="C87" s="7">
+        <v>1</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="H87" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="I87" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="J87" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K87" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="L87" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M87" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="N87" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="O87" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="P87" s="7"/>
+      <c r="Q87" s="7"/>
+      <c r="R87" s="7">
+        <v>0</v>
+      </c>
+      <c r="S87" s="7"/>
+      <c r="T87" s="7"/>
+      <c r="U87" s="7"/>
+      <c r="V87" s="7"/>
+      <c r="W87" s="7"/>
+      <c r="X87" s="7"/>
+      <c r="Y87" s="7"/>
+      <c r="Z87" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="AA87" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB87" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:28">
+      <c r="A88" s="3">
+        <v>86</v>
+      </c>
+      <c r="B88" s="3">
+        <v>2026100047</v>
+      </c>
+      <c r="C88" s="3">
+        <v>1</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="K88" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="L88" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="M88" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="N88" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="O88" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="P88" s="3"/>
+      <c r="Q88" s="3"/>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+      <c r="T88" s="3"/>
+      <c r="U88" s="3"/>
+      <c r="V88" s="3"/>
+      <c r="W88" s="3"/>
+      <c r="X88" s="3"/>
+      <c r="Y88" s="3"/>
+      <c r="Z88" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="AA88" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB88" s="3"/>
+    </row>
+    <row r="89" spans="1:28">
+      <c r="A89" s="7">
+        <v>87</v>
+      </c>
+      <c r="B89" s="7">
+        <v>2026100449</v>
+      </c>
+      <c r="C89" s="7">
+        <v>1</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G89" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="H89" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="I89" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="J89" s="7"/>
+      <c r="K89" s="7"/>
+      <c r="L89" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M89" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="N89" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="O89" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P89" s="7"/>
+      <c r="Q89" s="7"/>
+      <c r="R89" s="7">
+        <v>0</v>
+      </c>
+      <c r="S89" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T89" s="7"/>
+      <c r="U89" s="7"/>
+      <c r="V89" s="7"/>
+      <c r="W89" s="7"/>
+      <c r="X89" s="7"/>
+      <c r="Y89" s="7"/>
+      <c r="Z89" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA89" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB89" s="7"/>
+    </row>
+    <row r="90" spans="1:28">
+      <c r="A90" s="9"/>
+      <c r="B90" s="9"/>
+      <c r="C90" s="9"/>
+      <c r="D90" s="9"/>
+      <c r="E90" s="9"/>
+      <c r="F90" s="9"/>
+      <c r="G90" s="9"/>
+      <c r="H90" s="9"/>
+      <c r="I90" s="9"/>
+      <c r="J90" s="9"/>
+      <c r="K90" s="9"/>
+      <c r="L90" s="10"/>
+      <c r="M90" s="10"/>
+      <c r="N90" s="10"/>
+      <c r="O90" s="9"/>
+      <c r="P90" s="9"/>
+      <c r="Q90" s="9"/>
+      <c r="R90" s="9"/>
+      <c r="S90" s="9"/>
+      <c r="T90" s="9"/>
+      <c r="U90" s="9"/>
+      <c r="V90" s="9"/>
+      <c r="W90" s="9"/>
+      <c r="X90" s="9"/>
+      <c r="Y90" s="9"/>
+      <c r="Z90" s="10"/>
+      <c r="AA90" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="AB90" s="9">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
